--- a/media/exports/reports/2026-10/board.xlsx
+++ b/media/exports/reports/2026-10/board.xlsx
@@ -26,48 +26,58 @@
     <numFmt numFmtId="166" formatCode="0&quot;¢&quot;;[Red](0&quot;¢&quot;)"/>
     <numFmt numFmtId="167" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
@@ -100,46 +110,46 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -911,8 +921,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 board.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1341,8 +1351,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 board.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1568,8 +1578,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 board.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-10/board.xlsx
+++ b/media/exports/reports/2026-10/board.xlsx
@@ -655,7 +655,7 @@
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>• Unrestricted cash covers 1.8 months of spending, against a 3.0 months reserves target.
-• 4 grant(s) end within 6 months with $203,366 still to spend. Housing support: $97,842 left in 2 months ($48,921 a month needed, against $4,458 spent in October so far).
+• 4 grants end within 6 months with $203,366 still to spend. Housing support: $97,842 left in 2 months ($48,921 a month needed, against $4,458 spent in October so far).
 • Fundraising cost 9¢ per dollar in October so far: grants the cheapest (9¢), donations the dearest (10¢).</t>
         </is>
       </c>

--- a/media/exports/reports/2026-10/board.xlsx
+++ b/media/exports/reports/2026-10/board.xlsx
@@ -12,7 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="Surplus_October_so_far">'Report'!$B$8</definedName>
+    <definedName name="Surplus_deficit_year_to_date">'Report'!$B$9</definedName>
+    <definedName name="Unrestricted_cash_runway">'Report'!$B$10</definedName>
+    <definedName name="Cost_to_raise_a_dollar_October_so_far">'Report'!$B$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$F$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -74,12 +81,12 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="002F7A5D"/>
+      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="0025342A"/>
+      <color rgb="002F7A5D"/>
     </font>
   </fonts>
   <fills count="3">
@@ -126,17 +133,19 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -230,6 +239,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="board_Data" displayName="board_Data" ref="A5:F11" headerRowCount="1">
+  <autoFilter ref="A5:F11"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Program"/>
+    <tableColumn id="2" name="Spent to date"/>
+    <tableColumn id="3" name="Budget to date"/>
+    <tableColumn id="4" name="Against budget"/>
+    <tableColumn id="5" name="Still to spend"/>
+    <tableColumn id="6" name="Months left"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -542,14 +566,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -647,12 +671,244 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>Grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Spent to date</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Budget to date</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Against budget</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Still to spend</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Months left</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Housing support</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>$262,158</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>$300,000</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>87.4%</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>$97,842</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Volunteer coordinator</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>$21,429</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>$24,000</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>89.3%</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>$14,571</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Digital literacy</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>$60,302</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>$65,000</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>92.8%</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>$29,698</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Mental health first aid</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>$58,745</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>$70,000</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>83.9%</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>$61,255</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Youth outreach</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>$309,558</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>$320,000</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>96.7%</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>$170,442</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Community meals</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>$12,615</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>$16,000</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>78.8%</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>$35,385</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
           <t>What the board should note</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>• Unrestricted cash covers 1.8 months of spending, against a 3.0 months reserves target.
 • 4 grants end within 6 months with $203,366 still to spend. Housing support: $97,842 left in 2 months ($48,921 a month needed, against $4,458 spent in October so far).
@@ -660,241 +916,9 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Grants</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Program</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Spent to date</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Budget to date</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Against budget</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Still to spend</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Months left</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Housing support</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>$262,158</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>$300,000</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>87.4%</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>$97,842</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Volunteer coordinator</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>$21,429</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>$24,000</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>89.3%</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>$14,571</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Digital literacy</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>$60,302</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>$65,000</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>92.8%</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>$29,698</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Mental health first aid</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>$58,745</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>$70,000</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>83.9%</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>$61,255</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Youth outreach</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>$309,558</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>$320,000</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>$170,442</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Community meals</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>$12,615</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>$16,000</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>78.8%</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>$35,385</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
     <row r="24"/>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Decisions to make</t>
         </is>
@@ -914,15 +938,15 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -959,14 +983,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1376,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1391,14 +1415,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1603,14 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-10/board.xlsx
+++ b/media/exports/reports/2026-10/board.xlsx
@@ -17,7 +17,7 @@
     <definedName name="Unrestricted_cash_runway">'Report'!$B$10</definedName>
     <definedName name="Cost_to_raise_a_dollar_October_so_far">'Report'!$B$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$F$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$F$11</definedName>
   </definedNames>
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>Workings!B38</f>
+        <f>Workings!B39</f>
         <v/>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B11" s="9">
-        <f>Workings!B47</f>
+        <f>Workings!B48</f>
         <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>• Unrestricted cash covers 1.8 months of spending, against a 3.0 months reserves target.
+          <t>• Unrestricted cash covers 1.7 months of spending, against a 3.0 months reserves target.
 • 4 grants end within 6 months with $203,366 still to spend. Housing support: $97,842 left in 2 months ($48,921 a month needed, against $4,458 spent in October so far).
 • Fundraising cost 9¢ per dollar in October so far: grants the cheapest (9¢), donations the dearest (10¢).</t>
         </is>
@@ -946,7 +946,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -990,7 +990,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>(Cash at bank − unspent grant money) ÷ a month's cash spending</t>
+          <t>(Cash at bank − unspent grant money − GST and PAYG owed to the ATO) ÷ a month's cash spending</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="B34" s="16" t="n">
-        <v>438965</v>
+        <v>496243</v>
       </c>
     </row>
     <row r="35">
@@ -1261,122 +1261,132 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unrestricted cash</t>
-        </is>
-      </c>
-      <c r="B36" s="16">
-        <f>B34+B35</f>
-        <v/>
+          <t>Less GST and PAYG withheld owed to the ATO (paid with the BAS)</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n">
+        <v>-65523</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Unrestricted cash</t>
+        </is>
+      </c>
+      <c r="B37" s="16">
+        <f>B34+B35+B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Cash spending in September (expenses less depreciation)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B38" s="16" t="n">
         <v>162900</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Runway</t>
         </is>
       </c>
-      <c r="B38" s="19">
-        <f>B36/B37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>October is still in progress, so the rate of spending is September's. Reserves target: 3.0 months.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
+      <c r="B39" s="19">
+        <f>B37/B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>October is still in progress, so the rate of spending is September's, and what's owed to the ATO is at 30 September. Reserves target: 3.0 months.</t>
+        </is>
+      </c>
+    </row>
     <row r="41"/>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, October and September</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>Fundraising costs ÷ money raised, in cents</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr"/>
-      <c r="B44" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Oct 26</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Fundraising costs</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n">
-        <v>1331</v>
-      </c>
-      <c r="C45" s="16" t="n">
-        <v>29400</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Fundraising costs</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="n">
+        <v>1331</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>29400</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Money raised</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n">
+      <c r="B47" s="16" t="n">
         <v>14301</v>
       </c>
-      <c r="C46" s="16" t="n">
+      <c r="C47" s="16" t="n">
         <v>146500</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Cents per dollar</t>
         </is>
       </c>
-      <c r="B47" s="20">
-        <f>B45/B46*100</f>
-        <v/>
-      </c>
-      <c r="C47" s="20">
-        <f>C45/C46*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48"/>
+      <c r="B48" s="20">
+        <f>B46/B47*100</f>
+        <v/>
+      </c>
+      <c r="C48" s="20">
+        <f>C46/C47*100</f>
+        <v/>
+      </c>
+    </row>
     <row r="49"/>
     <row r="50"/>
+    <row r="51"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1422,7 +1432,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1613,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-10/board.xlsx
+++ b/media/exports/reports/2026-10/board.xlsx
@@ -12,11 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Surplus_October_so_far">'Report'!$B$8</definedName>
-    <definedName name="Surplus_deficit_year_to_date">'Report'!$B$9</definedName>
-    <definedName name="Unrestricted_cash_runway">'Report'!$B$10</definedName>
-    <definedName name="Cost_to_raise_a_dollar_October_so_far">'Report'!$B$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$F$26</definedName>
+    <definedName name="Surplus_October_so_far">'Report'!$B$9</definedName>
+    <definedName name="Surplus_deficit_year_to_date">'Report'!$B$10</definedName>
+    <definedName name="Unrestricted_cash_runway">'Report'!$B$11</definedName>
+    <definedName name="Cost_to_raise_a_dollar_October_so_far">'Report'!$B$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$F$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$F$11</definedName>
@@ -57,6 +57,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -77,11 +82,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -119,26 +119,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -146,19 +149,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -545,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -573,7 +576,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -581,334 +584,341 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: A ($10,737) deficit in October so far, 1.7 months of runway, and 4 grants ending within 6 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>A one-page board summary for October 2026 to date: the result, the money, the risks, and the decisions to make. The full statements are in the downloads.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Surplus, October so far</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>Workings!B10</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>September $10,380</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Surplus (deficit), year to date</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>Workings!B27</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Jul to Oct 2026</t>
+          <t>Surplus, October so far</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>Workings!B10</f>
+        <v/>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>September $10,380</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unrestricted cash runway</t>
-        </is>
-      </c>
-      <c r="B10" s="8">
-        <f>Workings!B39</f>
-        <v/>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>reserves target 3.0 months</t>
+          <t>Surplus (deficit), year to date</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>Workings!B27</f>
+        <v/>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Jul to Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Unrestricted cash runway</t>
+        </is>
+      </c>
+      <c r="B11" s="9">
+        <f>Workings!B39</f>
+        <v/>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>reserves target 3.0 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Cost to raise a dollar, October so far</t>
         </is>
       </c>
-      <c r="B11" s="9">
+      <c r="B12" s="10">
         <f>Workings!B48</f>
         <v/>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>September 20¢</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Spent to date</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Budget to date</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Against budget</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Months left</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Housing support</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>$262,158</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>$300,000</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>87.4%</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>$97,842</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>$21,429</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>$24,000</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>89.3%</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>$14,571</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>$60,302</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>$65,000</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>92.8%</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>$29,698</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Mental health first aid</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>$58,745</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>$70,000</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>83.9%</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>$61,255</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>$309,558</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>$320,000</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>96.7%</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>$170,442</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Community meals</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>$12,615</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>$16,000</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>78.8%</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>$35,385</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>What the board should note</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>• Unrestricted cash covers 1.7 months of spending, against a 3.0 months reserves target.
 • 4 grants end within 6 months with $203,366 still to spend. Housing support: $97,842 left in 2 months ($48,921 a month needed, against $4,458 spent in October so far).
@@ -916,16 +926,16 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Decisions to make</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>• Housing support: lift spending to $48,921 a month, or ask State Housing Program about carrying the balance over.
 • Reserves: how much of each month's surplus goes to reserves, and by when the target is reached.
@@ -933,27 +943,28 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28"/>
+    <row r="29"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="24" min="0" max="16383" man="1"/>
+    <brk id="25" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -990,33 +1001,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Surplus, October and September</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Income less expenses</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Oct 26</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -1028,10 +1039,10 @@
           <t>Income</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>17802</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>176180</v>
       </c>
     </row>
@@ -1041,24 +1052,24 @@
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>28539</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>165800</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Surplus</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>B8-B9</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>C8-C9</f>
         <v/>
       </c>
@@ -1073,22 +1084,22 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Year to date (Jul to Oct 2026)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Income less expenses, financial year to date</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>FY2027 to date</t>
         </is>
@@ -1100,7 +1111,7 @@
           <t>Income, July</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>112398</v>
       </c>
     </row>
@@ -1110,7 +1121,7 @@
           <t>Income, August</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>120350</v>
       </c>
     </row>
@@ -1120,7 +1131,7 @@
           <t>Income, September</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>176180</v>
       </c>
     </row>
@@ -1130,7 +1141,7 @@
           <t>Income, October</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>17802</v>
       </c>
     </row>
@@ -1140,7 +1151,7 @@
           <t>Income, year to date</t>
         </is>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="17">
         <f>B17+B18+B19+B20</f>
         <v/>
       </c>
@@ -1151,7 +1162,7 @@
           <t>Expenses, July</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>137818</v>
       </c>
     </row>
@@ -1161,7 +1172,7 @@
           <t>Expenses, August</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>144100</v>
       </c>
     </row>
@@ -1171,7 +1182,7 @@
           <t>Expenses, September</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>165800</v>
       </c>
     </row>
@@ -1181,7 +1192,7 @@
           <t>Expenses, October</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>28539</v>
       </c>
     </row>
@@ -1191,18 +1202,18 @@
           <t>Expenses, year to date</t>
         </is>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <f>B22+B23+B24+B25</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Surplus (deficit), year to date</t>
         </is>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="19">
         <f>B21-B26</f>
         <v/>
       </c>
@@ -1217,22 +1228,22 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Unrestricted cash runway, October 2026</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>(Cash at bank − unspent grant money − GST and PAYG owed to the ATO) ÷ a month's cash spending</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -1244,7 +1255,7 @@
           <t>Cash at bank</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>496243</v>
       </c>
     </row>
@@ -1254,7 +1265,7 @@
           <t>Less unspent grant money (belongs to funders' programs)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>-149053</v>
       </c>
     </row>
@@ -1264,7 +1275,7 @@
           <t>Less GST and PAYG withheld owed to the ATO (paid with the BAS)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>-65523</v>
       </c>
     </row>
@@ -1274,7 +1285,7 @@
           <t>Unrestricted cash</t>
         </is>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <f>B34+B35+B36</f>
         <v/>
       </c>
@@ -1285,17 +1296,17 @@
           <t>Cash spending in September (expenses less depreciation)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>162900</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>Runway</t>
         </is>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="20">
         <f>B37/B38</f>
         <v/>
       </c>
@@ -1310,27 +1321,27 @@
     <row r="41"/>
     <row r="42"/>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, October and September</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Fundraising costs ÷ money raised, in cents</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr"/>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Oct 26</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -1342,10 +1353,10 @@
           <t>Fundraising costs</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n">
+      <c r="B46" s="17" t="n">
         <v>1331</v>
       </c>
-      <c r="C46" s="16" t="n">
+      <c r="C46" s="17" t="n">
         <v>29400</v>
       </c>
     </row>
@@ -1355,24 +1366,24 @@
           <t>Money raised</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>14301</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>146500</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>Cents per dollar</t>
         </is>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="21">
         <f>B46/B47*100</f>
         <v/>
       </c>
-      <c r="C48" s="20">
+      <c r="C48" s="21">
         <f>C46/C47*100</f>
         <v/>
       </c>
@@ -1386,7 +1397,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1432,178 +1443,178 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:56am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Spent to date</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Budget to date</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Against budget</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Still to spend</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Months left</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Housing support</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>262158</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>300000</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="23">
         <f>B6/C6</f>
         <v/>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>97842</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>21429</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>24000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="23">
         <f>B7/C7</f>
         <v/>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>14571</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>60302</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>65000</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="23">
         <f>B8/C8</f>
         <v/>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>29698</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Mental health first aid</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>58745</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>70000</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="23">
         <f>B9/C9</f>
         <v/>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>61255</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Youth outreach</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>309558</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>320000</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="23">
         <f>B10/C10</f>
         <v/>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>170442</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Community meals</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>12615</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>16000</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <f>B11/C11</f>
         <v/>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>35385</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1613,7 +1624,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:56am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 board.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
